--- a/data-xlsx/data.xlsx
+++ b/data-xlsx/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pdp\MyProjects\GitHub\MyInvest\data-xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854A071A-CACC-43F4-925F-B6911857C958}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E73482CB-7406-41EA-9300-C9F69E06C280}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21909" windowHeight="9266" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21909" windowHeight="9266" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Счета" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="143">
   <si>
     <t>id</t>
   </si>
@@ -4605,7 +4605,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="20.53515625" style="1" customWidth="1"/>
@@ -5503,6 +5503,20 @@
         <v>10</v>
       </c>
     </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A56" s="11">
+        <v>46095</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C56" s="1">
+        <v>21528.68</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data-xlsx/data.xlsx
+++ b/data-xlsx/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pdp\MyProjects\GitHub\MyInvest\data-xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E73482CB-7406-41EA-9300-C9F69E06C280}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9A31E8-E8A6-4C6F-8B0A-EA9F8A0BDD16}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21909" windowHeight="9266" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21909" windowHeight="9266" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Счета" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="142">
   <si>
     <t>id</t>
   </si>
@@ -264,9 +264,6 @@
   </si>
   <si>
     <t>AKMB-I</t>
-  </si>
-  <si>
-    <t>AKMB в инвесткопилке</t>
   </si>
   <si>
     <t>SAFE</t>
@@ -970,7 +967,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="11.765625" style="5" bestFit="1" customWidth="1"/>
@@ -1005,16 +1002,16 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>142</v>
-      </c>
       <c r="I1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
@@ -1099,10 +1096,10 @@
     </row>
     <row r="6" spans="1:10" ht="15.9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -1111,13 +1108,13 @@
         <v>36</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:10" ht="15.9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
@@ -1129,10 +1126,10 @@
         <v>31</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.4">
@@ -1281,7 +1278,7 @@
         <v>75</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.4">
@@ -1303,10 +1300,10 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
         <v>27</v>
@@ -1315,35 +1312,44 @@
         <v>10</v>
       </c>
       <c r="E17" t="s">
-        <v>79</v>
-      </c>
-      <c r="F17" s="5" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
       </c>
-      <c r="E18" t="s">
-        <v>81</v>
+      <c r="E18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2400</v>
+      </c>
+      <c r="H18" s="1">
+        <v>2800</v>
+      </c>
+      <c r="J18" s="4">
+        <v>46357</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
         <v>41</v>
@@ -1351,83 +1357,82 @@
       <c r="D19" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="F19" t="s">
-        <v>42</v>
+      <c r="E19" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="G19" s="1">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="H19" s="1">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="J19" s="4">
         <v>46357</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="A20" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D20" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>48</v>
+      <c r="D20" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G20" s="1">
-        <v>2600</v>
+        <v>14.43</v>
       </c>
       <c r="H20" s="1">
-        <v>2600</v>
+        <v>15.6</v>
       </c>
       <c r="J20" s="4">
-        <v>46357</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A21" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="A21" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G21" s="1">
-        <v>14.43</v>
-      </c>
-      <c r="H21" s="1">
-        <v>15.6</v>
-      </c>
-      <c r="J21" s="4">
-        <v>46173</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A22" s="8" t="s">
+      <c r="D21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="8" t="s">
         <v>69</v>
       </c>
+      <c r="F21" s="8"/>
+      <c r="G21" s="9">
+        <v>3700</v>
+      </c>
+      <c r="H21" s="9">
+        <v>4800</v>
+      </c>
+      <c r="I21" s="9"/>
+      <c r="J21" s="10">
+        <v>46447</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="A22" s="7" t="s">
+        <v>123</v>
+      </c>
       <c r="B22" s="8" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>41</v>
@@ -1435,17 +1440,17 @@
       <c r="D22" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="8" t="s">
-        <v>69</v>
+      <c r="E22" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="9">
-        <v>3700</v>
+        <v>400</v>
       </c>
       <c r="H22" s="9">
-        <v>4800</v>
-      </c>
-      <c r="I22" s="9"/>
+        <v>420</v>
+      </c>
+      <c r="I22" s="8"/>
       <c r="J22" s="10">
         <v>46447</v>
       </c>
@@ -1455,7 +1460,7 @@
         <v>124</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>41</v>
@@ -1468,22 +1473,22 @@
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="9">
-        <v>400</v>
-      </c>
-      <c r="H23" s="9">
-        <v>420</v>
-      </c>
-      <c r="I23" s="8"/>
+        <v>64</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="I23" s="9"/>
       <c r="J23" s="10">
         <v>46447</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A24" s="7" t="s">
-        <v>125</v>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A24" s="8" t="s">
+        <v>133</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>41</v>
@@ -1491,78 +1496,50 @@
       <c r="D24" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>125</v>
+      <c r="E24" s="8" t="s">
+        <v>133</v>
       </c>
       <c r="F24" s="8"/>
-      <c r="G24" s="9">
-        <v>64</v>
+      <c r="G24" s="9" t="s">
+        <v>136</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="I24" s="9"/>
+        <v>136</v>
+      </c>
+      <c r="I24" s="8"/>
       <c r="J24" s="10">
         <v>46447</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C25" s="8" t="s">
+      <c r="B25" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="8" t="s">
+      <c r="D25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="F25" s="8"/>
-      <c r="G25" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="I25" s="8"/>
-      <c r="J25" s="10">
+      <c r="G25" s="1">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1.04</v>
+      </c>
+      <c r="I25" s="1"/>
+      <c r="J25" s="2">
         <v>46447</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A26" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="G26" s="1">
-        <v>1</v>
-      </c>
-      <c r="H26" s="1">
-        <v>1.04</v>
-      </c>
-      <c r="I26" s="1"/>
-      <c r="J26" s="2">
-        <v>46447</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState ref="A1:J24">
+  <sortState ref="A1:J23">
     <sortCondition ref="C1"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1590,37 +1567,37 @@
         <v>22</v>
       </c>
       <c r="B1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" t="s">
         <v>83</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>84</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="G1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="I1" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="G1" t="s">
-        <v>128</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>86</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>87</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>88</v>
-      </c>
-      <c r="L1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.4">
@@ -1649,7 +1626,7 @@
         <v>46148</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
@@ -1680,7 +1657,7 @@
         <v>46107</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
@@ -1711,7 +1688,7 @@
         <v>46097</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
@@ -1742,7 +1719,7 @@
         <v>46120</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
@@ -1773,7 +1750,7 @@
         <v>46134</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
@@ -1803,7 +1780,7 @@
         <v>46112</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
@@ -1834,12 +1811,12 @@
         <v>46176</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B9" s="5">
         <v>100</v>
@@ -1864,12 +1841,12 @@
         <v>46111</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B10" s="5">
         <v>1000</v>
@@ -1893,7 +1870,7 @@
         <v>46099</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1927,40 +1904,40 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>4</v>
@@ -1983,7 +1960,7 @@
         <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E2" s="1">
         <v>1287</v>
@@ -2009,7 +1986,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -2035,7 +2012,7 @@
         <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E4" s="1">
         <v>1255</v>
@@ -2070,7 +2047,7 @@
         <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E5" s="1">
         <v>20</v>
@@ -2102,7 +2079,7 @@
         <v>6</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -2128,7 +2105,7 @@
         <v>25</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E7" s="1">
         <v>1100</v>
@@ -2163,7 +2140,7 @@
         <v>25</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E8" s="1">
         <v>100</v>
@@ -2198,7 +2175,7 @@
         <v>25</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E9" s="1">
         <v>1000</v>
@@ -2233,7 +2210,7 @@
         <v>25</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E10" s="1">
         <v>1100</v>
@@ -2265,7 +2242,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -2288,7 +2265,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -2314,7 +2291,7 @@
         <v>28</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -2352,7 +2329,7 @@
         <v>34</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -2390,7 +2367,7 @@
         <v>40</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -2425,7 +2402,7 @@
         <v>43</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E16" s="1">
         <v>34</v>
@@ -2457,7 +2434,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>10</v>
@@ -2483,7 +2460,7 @@
         <v>46</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -2518,7 +2495,7 @@
         <v>49</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -2556,7 +2533,7 @@
         <v>53</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -2594,7 +2571,7 @@
         <v>43</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E21" s="1">
         <v>9</v>
@@ -2630,7 +2607,7 @@
         <v>43</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E22" s="1">
         <v>9</v>
@@ -2663,7 +2640,7 @@
         <v>14</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>10</v>
@@ -2689,7 +2666,7 @@
         <v>77</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E24" s="1">
         <v>4</v>
@@ -2725,7 +2702,7 @@
         <v>75</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -2760,7 +2737,7 @@
         <v>73</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E26" s="1">
         <v>96</v>
@@ -2792,7 +2769,7 @@
         <v>14</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>10</v>
@@ -2807,7 +2784,7 @@
         <v>16</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.4">
@@ -2821,7 +2798,7 @@
         <v>71</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E28" s="1">
         <v>5</v>
@@ -2856,7 +2833,7 @@
         <v>71</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
@@ -2891,7 +2868,7 @@
         <v>73</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E30" s="1">
         <v>64</v>
@@ -2923,7 +2900,7 @@
         <v>14</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>10</v>
@@ -2949,7 +2926,7 @@
         <v>77</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E32" s="1">
         <v>6</v>
@@ -2984,7 +2961,7 @@
         <v>75</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E33" s="1">
         <v>8</v>
@@ -3019,7 +2996,7 @@
         <v>69</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
@@ -3054,7 +3031,7 @@
         <v>66</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E35" s="1">
         <v>1000</v>
@@ -3089,7 +3066,7 @@
         <v>71</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E36" s="1">
         <v>6</v>
@@ -3124,7 +3101,7 @@
         <v>73</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E37" s="1">
         <v>147</v>
@@ -3159,7 +3136,7 @@
         <v>73</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E38" s="1">
         <v>50</v>
@@ -3191,7 +3168,7 @@
         <v>14</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>10</v>
@@ -3217,7 +3194,7 @@
         <v>69</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -3249,7 +3226,7 @@
         <v>14</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>10</v>
@@ -3264,7 +3241,7 @@
         <v>16</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.4">
@@ -3278,7 +3255,7 @@
         <v>63</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -3313,7 +3290,7 @@
         <v>77</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E43" s="1">
         <v>10</v>
@@ -3348,7 +3325,7 @@
         <v>61</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E44" s="1">
         <v>100</v>
@@ -3383,7 +3360,7 @@
         <v>57</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -3418,7 +3395,7 @@
         <v>49</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -3450,7 +3427,7 @@
         <v>14</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>10</v>
@@ -3465,7 +3442,7 @@
         <v>16</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.4">
@@ -3476,10 +3453,10 @@
         <v>17</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>10</v>
@@ -3502,7 +3479,7 @@
         <v>20</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E49" s="1">
         <v>24829</v>
@@ -3528,7 +3505,7 @@
         <v>20</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E50" s="1">
         <v>22066</v>
@@ -3557,7 +3534,7 @@
         <v>34</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -3589,7 +3566,7 @@
         <v>14</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>10</v>
@@ -3615,7 +3592,7 @@
         <v>75</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E53" s="1">
         <v>12</v>
@@ -3650,7 +3627,7 @@
         <v>73</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E54" s="1">
         <v>50</v>
@@ -3685,7 +3662,7 @@
         <v>75</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E55" s="1">
         <v>33</v>
@@ -3720,7 +3697,7 @@
         <v>73</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E56" s="1">
         <v>60</v>
@@ -3752,7 +3729,7 @@
         <v>20</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L57" s="1">
         <f>194.52+285.76+81.59+255+39.29</f>
@@ -3776,7 +3753,7 @@
         <v>53</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E58" s="1">
         <v>1</v>
@@ -3808,7 +3785,7 @@
         <v>6</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>10</v>
@@ -3831,7 +3808,7 @@
         <v>11</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>10</v>
@@ -3857,7 +3834,7 @@
         <v>25</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E61" s="1">
         <v>1080</v>
@@ -3890,7 +3867,7 @@
         <v>20</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L62" s="1">
         <v>5314.34</v>
@@ -3910,7 +3887,7 @@
         <v>14</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>10</v>
@@ -3925,7 +3902,7 @@
         <v>16</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.4">
@@ -3936,7 +3913,7 @@
         <v>14</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>10</v>
@@ -3951,7 +3928,7 @@
         <v>16</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.4">
@@ -3962,7 +3939,7 @@
         <v>14</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>10</v>
@@ -3985,10 +3962,10 @@
         <v>11</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -4023,10 +4000,10 @@
         <v>11</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E67" s="1">
         <v>1</v>
@@ -4062,10 +4039,10 @@
         <v>11</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E68" s="1">
         <v>10</v>
@@ -4097,10 +4074,10 @@
         <v>11</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E69" s="1">
         <v>11</v>
@@ -4135,7 +4112,7 @@
         <v>43</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E70" s="1">
         <v>3</v>
@@ -4170,7 +4147,7 @@
         <v>69</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -4202,10 +4179,10 @@
         <v>14</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -4240,7 +4217,7 @@
         <v>73</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E73" s="1">
         <v>208</v>
@@ -4275,7 +4252,7 @@
         <v>73</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E74" s="1">
         <v>32</v>
@@ -4310,7 +4287,7 @@
         <v>73</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E75" s="1">
         <v>5</v>
@@ -4342,10 +4319,10 @@
         <v>14</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E76" s="1">
         <v>3000</v>
@@ -4377,10 +4354,10 @@
         <v>14</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E77" s="1">
         <v>1000</v>
@@ -4412,10 +4389,10 @@
         <v>14</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E78" s="1">
         <v>1000</v>
@@ -4447,10 +4424,10 @@
         <v>17</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L79" s="1">
         <v>1400</v>
@@ -4470,7 +4447,7 @@
         <v>14</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L80" s="1">
         <v>1000</v>
@@ -4493,7 +4470,7 @@
         <v>73</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E81" s="1">
         <v>174</v>
@@ -4525,10 +4502,10 @@
         <v>14</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E82" s="1">
         <v>1000</v>
@@ -4561,7 +4538,7 @@
         <v>20</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L83" s="1">
         <f>27.6+58.69</f>
@@ -4582,10 +4559,10 @@
         <v>17</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L84" s="1">
         <v>2800</v>
@@ -4620,25 +4597,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
@@ -5167,7 +5144,7 @@
         <v>46075</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C34" s="1">
         <v>24191.29</v>
@@ -5195,7 +5172,7 @@
         <v>46075</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C36" s="1">
         <v>26033.46</v>
@@ -5238,7 +5215,7 @@
         <v>31</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.4">
@@ -5261,7 +5238,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.4">
@@ -5469,7 +5446,7 @@
         <v>46082</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>10</v>
@@ -5494,7 +5471,7 @@
         <v>46082</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C55" s="1">
         <v>26282.52</v>

--- a/data-xlsx/data.xlsx
+++ b/data-xlsx/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pdp\MyProjects\GitHub\MyInvest\data-xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9A31E8-E8A6-4C6F-8B0A-EA9F8A0BDD16}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0519402D-837C-4FAA-9E00-13C56346C16F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21909" windowHeight="9266" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21909" windowHeight="9266" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Счета" sheetId="1" r:id="rId1"/>
@@ -206,9 +206,6 @@
     <t>bond_gov</t>
   </si>
   <si>
-    <t>RU000A1038V6</t>
-  </si>
-  <si>
     <t>AFKS</t>
   </si>
   <si>
@@ -221,9 +218,6 @@
     <t>ОФЗ Руб 03.10.2040</t>
   </si>
   <si>
-    <t>RU000A10D533</t>
-  </si>
-  <si>
     <t>РФ ЗО 30 Д</t>
   </si>
   <si>
@@ -450,6 +444,12 @@
   </si>
   <si>
     <t>target_max</t>
+  </si>
+  <si>
+    <t>SU26254RMFS1</t>
+  </si>
+  <si>
+    <t>SU26238RMFS4</t>
   </si>
 </sst>
 </file>
@@ -974,7 +974,7 @@
     <col min="2" max="2" width="37.921875" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.84375" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.4609375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.15234375" style="5" customWidth="1"/>
     <col min="6" max="6" width="39.84375" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.921875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.15234375" style="5" bestFit="1" customWidth="1"/>
@@ -1002,16 +1002,16 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
@@ -1096,10 +1096,10 @@
     </row>
     <row r="6" spans="1:10" ht="15.9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -1108,13 +1108,13 @@
         <v>36</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:10" ht="15.9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
@@ -1126,10 +1126,10 @@
         <v>31</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.4">
@@ -1146,7 +1146,7 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>60</v>
+        <v>141</v>
       </c>
       <c r="F8" t="s">
         <v>58</v>
@@ -1154,10 +1154,10 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" t="s">
         <v>63</v>
-      </c>
-      <c r="B9" t="s">
-        <v>64</v>
       </c>
       <c r="C9" t="s">
         <v>59</v>
@@ -1166,16 +1166,16 @@
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
         <v>59</v>
@@ -1184,7 +1184,7 @@
         <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F10"/>
     </row>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
@@ -1239,15 +1239,15 @@
         <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
         <v>27</v>
@@ -1256,17 +1256,17 @@
         <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
         <v>27</v>
@@ -1275,18 +1275,18 @@
         <v>10</v>
       </c>
       <c r="E15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
         <v>27</v>
@@ -1295,15 +1295,15 @@
         <v>10</v>
       </c>
       <c r="E16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
         <v>27</v>
@@ -1312,7 +1312,7 @@
         <v>10</v>
       </c>
       <c r="E17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.4">
@@ -1375,10 +1375,10 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>62</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>41</v>
@@ -1387,7 +1387,7 @@
         <v>10</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G20" s="1">
         <v>14.43</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>41</v>
@@ -1413,7 +1413,7 @@
         <v>10</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="9">
@@ -1429,10 +1429,10 @@
     </row>
     <row r="22" spans="1:10" ht="15.9" x14ac:dyDescent="0.45">
       <c r="A22" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>41</v>
@@ -1441,7 +1441,7 @@
         <v>10</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="9">
@@ -1457,10 +1457,10 @@
     </row>
     <row r="23" spans="1:10" ht="15.9" x14ac:dyDescent="0.45">
       <c r="A23" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>41</v>
@@ -1469,14 +1469,14 @@
         <v>10</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="9">
         <v>64</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I23" s="9"/>
       <c r="J23" s="10">
@@ -1485,10 +1485,10 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>41</v>
@@ -1497,14 +1497,14 @@
         <v>10</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F24" s="8"/>
       <c r="G24" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I24" s="8"/>
       <c r="J24" s="10">
@@ -1513,10 +1513,10 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>41</v>
@@ -1525,7 +1525,7 @@
         <v>10</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G25" s="1">
         <v>1</v>
@@ -1567,37 +1567,37 @@
         <v>22</v>
       </c>
       <c r="B1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" t="s">
         <v>82</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="I1" t="s">
         <v>83</v>
       </c>
-      <c r="D1" t="s">
+      <c r="J1" t="s">
         <v>84</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G1" t="s">
-        <v>127</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>85</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>86</v>
-      </c>
-      <c r="K1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.4">
@@ -1626,7 +1626,7 @@
         <v>46148</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
@@ -1657,7 +1657,7 @@
         <v>46107</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
@@ -1688,7 +1688,7 @@
         <v>46097</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
@@ -1719,12 +1719,12 @@
         <v>46120</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B6">
         <v>1000</v>
@@ -1750,12 +1750,12 @@
         <v>46134</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B7">
         <v>4.4999999999999998E-2</v>
@@ -1780,7 +1780,7 @@
         <v>46112</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
@@ -1811,12 +1811,12 @@
         <v>46176</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B9" s="5">
         <v>100</v>
@@ -1841,12 +1841,12 @@
         <v>46111</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B10" s="5">
         <v>1000</v>
@@ -1870,7 +1870,7 @@
         <v>46099</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1904,40 +1904,40 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>4</v>
@@ -1960,7 +1960,7 @@
         <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E2" s="1">
         <v>1287</v>
@@ -1986,7 +1986,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -2012,7 +2012,7 @@
         <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E4" s="1">
         <v>1255</v>
@@ -2047,7 +2047,7 @@
         <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E5" s="1">
         <v>20</v>
@@ -2079,7 +2079,7 @@
         <v>6</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -2105,7 +2105,7 @@
         <v>25</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E7" s="1">
         <v>1100</v>
@@ -2140,7 +2140,7 @@
         <v>25</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E8" s="1">
         <v>100</v>
@@ -2175,7 +2175,7 @@
         <v>25</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E9" s="1">
         <v>1000</v>
@@ -2210,7 +2210,7 @@
         <v>25</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E10" s="1">
         <v>1100</v>
@@ -2242,7 +2242,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -2265,7 +2265,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -2291,7 +2291,7 @@
         <v>28</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -2329,7 +2329,7 @@
         <v>34</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -2367,7 +2367,7 @@
         <v>40</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -2402,7 +2402,7 @@
         <v>43</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E16" s="1">
         <v>34</v>
@@ -2434,7 +2434,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>10</v>
@@ -2460,7 +2460,7 @@
         <v>46</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -2495,7 +2495,7 @@
         <v>49</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -2533,7 +2533,7 @@
         <v>53</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -2571,7 +2571,7 @@
         <v>43</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E21" s="1">
         <v>9</v>
@@ -2607,7 +2607,7 @@
         <v>43</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E22" s="1">
         <v>9</v>
@@ -2640,7 +2640,7 @@
         <v>14</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>10</v>
@@ -2663,10 +2663,10 @@
         <v>14</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E24" s="1">
         <v>4</v>
@@ -2699,10 +2699,10 @@
         <v>14</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -2734,10 +2734,10 @@
         <v>14</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E26" s="1">
         <v>96</v>
@@ -2769,7 +2769,7 @@
         <v>14</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>10</v>
@@ -2784,7 +2784,7 @@
         <v>16</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.4">
@@ -2795,10 +2795,10 @@
         <v>14</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E28" s="1">
         <v>5</v>
@@ -2830,10 +2830,10 @@
         <v>14</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
@@ -2865,10 +2865,10 @@
         <v>14</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E30" s="1">
         <v>64</v>
@@ -2900,7 +2900,7 @@
         <v>14</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>10</v>
@@ -2923,10 +2923,10 @@
         <v>14</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E32" s="1">
         <v>6</v>
@@ -2958,10 +2958,10 @@
         <v>14</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E33" s="1">
         <v>8</v>
@@ -2993,10 +2993,10 @@
         <v>14</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
@@ -3028,10 +3028,10 @@
         <v>14</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E35" s="1">
         <v>1000</v>
@@ -3063,10 +3063,10 @@
         <v>14</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E36" s="1">
         <v>6</v>
@@ -3098,10 +3098,10 @@
         <v>14</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E37" s="1">
         <v>147</v>
@@ -3133,10 +3133,10 @@
         <v>14</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E38" s="1">
         <v>50</v>
@@ -3168,7 +3168,7 @@
         <v>14</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>10</v>
@@ -3191,10 +3191,10 @@
         <v>14</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -3226,7 +3226,7 @@
         <v>14</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>10</v>
@@ -3241,7 +3241,7 @@
         <v>16</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.4">
@@ -3252,10 +3252,10 @@
         <v>14</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -3287,10 +3287,10 @@
         <v>14</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E43" s="1">
         <v>10</v>
@@ -3322,10 +3322,10 @@
         <v>14</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E44" s="1">
         <v>100</v>
@@ -3360,7 +3360,7 @@
         <v>57</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -3395,7 +3395,7 @@
         <v>49</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -3427,7 +3427,7 @@
         <v>14</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>10</v>
@@ -3442,7 +3442,7 @@
         <v>16</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.4">
@@ -3453,10 +3453,10 @@
         <v>17</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>10</v>
@@ -3479,7 +3479,7 @@
         <v>20</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E49" s="1">
         <v>24829</v>
@@ -3505,7 +3505,7 @@
         <v>20</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E50" s="1">
         <v>22066</v>
@@ -3534,7 +3534,7 @@
         <v>34</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -3566,7 +3566,7 @@
         <v>14</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>10</v>
@@ -3589,10 +3589,10 @@
         <v>14</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E53" s="1">
         <v>12</v>
@@ -3624,10 +3624,10 @@
         <v>14</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E54" s="1">
         <v>50</v>
@@ -3659,10 +3659,10 @@
         <v>14</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E55" s="1">
         <v>33</v>
@@ -3694,10 +3694,10 @@
         <v>14</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E56" s="1">
         <v>60</v>
@@ -3729,7 +3729,7 @@
         <v>20</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L57" s="1">
         <f>194.52+285.76+81.59+255+39.29</f>
@@ -3753,7 +3753,7 @@
         <v>53</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E58" s="1">
         <v>1</v>
@@ -3785,7 +3785,7 @@
         <v>6</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>10</v>
@@ -3808,7 +3808,7 @@
         <v>11</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>10</v>
@@ -3834,7 +3834,7 @@
         <v>25</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E61" s="1">
         <v>1080</v>
@@ -3867,7 +3867,7 @@
         <v>20</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L62" s="1">
         <v>5314.34</v>
@@ -3887,7 +3887,7 @@
         <v>14</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>10</v>
@@ -3902,7 +3902,7 @@
         <v>16</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.4">
@@ -3913,7 +3913,7 @@
         <v>14</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>10</v>
@@ -3928,7 +3928,7 @@
         <v>16</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.4">
@@ -3939,7 +3939,7 @@
         <v>14</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>10</v>
@@ -3962,10 +3962,10 @@
         <v>11</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -4000,10 +4000,10 @@
         <v>11</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E67" s="1">
         <v>1</v>
@@ -4039,10 +4039,10 @@
         <v>11</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E68" s="1">
         <v>10</v>
@@ -4074,10 +4074,10 @@
         <v>11</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E69" s="1">
         <v>11</v>
@@ -4112,7 +4112,7 @@
         <v>43</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E70" s="1">
         <v>3</v>
@@ -4144,10 +4144,10 @@
         <v>14</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -4179,10 +4179,10 @@
         <v>14</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -4214,10 +4214,10 @@
         <v>14</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E73" s="1">
         <v>208</v>
@@ -4249,10 +4249,10 @@
         <v>14</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E74" s="1">
         <v>32</v>
@@ -4284,10 +4284,10 @@
         <v>14</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E75" s="1">
         <v>5</v>
@@ -4319,10 +4319,10 @@
         <v>14</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E76" s="1">
         <v>3000</v>
@@ -4354,10 +4354,10 @@
         <v>14</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E77" s="1">
         <v>1000</v>
@@ -4389,10 +4389,10 @@
         <v>14</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E78" s="1">
         <v>1000</v>
@@ -4424,10 +4424,10 @@
         <v>17</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L79" s="1">
         <v>1400</v>
@@ -4447,7 +4447,7 @@
         <v>14</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L80" s="1">
         <v>1000</v>
@@ -4467,10 +4467,10 @@
         <v>14</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E81" s="1">
         <v>174</v>
@@ -4502,10 +4502,10 @@
         <v>14</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E82" s="1">
         <v>1000</v>
@@ -4538,7 +4538,7 @@
         <v>20</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L83" s="1">
         <f>27.6+58.69</f>
@@ -4559,10 +4559,10 @@
         <v>17</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L84" s="1">
         <v>2800</v>
@@ -4597,25 +4597,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
@@ -4782,7 +4782,7 @@
         <v>46068</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11" s="12">
         <v>1380</v>
@@ -4796,7 +4796,7 @@
         <v>46068</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C12" s="12">
         <v>927.49</v>
@@ -4810,7 +4810,7 @@
         <v>46068</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C13" s="12">
         <v>3532.19</v>
@@ -4824,7 +4824,7 @@
         <v>46068</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C14" s="12">
         <v>10131</v>
@@ -4838,7 +4838,7 @@
         <v>46068</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C15" s="1">
         <f>129.11*13</f>
@@ -4853,7 +4853,7 @@
         <v>46068</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C16" s="1">
         <f>1.8938*357</f>
@@ -4868,7 +4868,7 @@
         <v>46068</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C17" s="1">
         <f>278.63*10</f>
@@ -5045,7 +5045,7 @@
         <v>46075</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C27" s="1">
         <v>1418.4</v>
@@ -5059,7 +5059,7 @@
         <v>46075</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C28" s="1">
         <v>926.48</v>
@@ -5073,7 +5073,7 @@
         <v>46075</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C29" s="1">
         <v>3875.47</v>
@@ -5087,7 +5087,7 @@
         <v>46075</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C30" s="1">
         <v>10551</v>
@@ -5101,7 +5101,7 @@
         <v>46075</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C31" s="1">
         <v>1679.86</v>
@@ -5115,7 +5115,7 @@
         <v>46075</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C32" s="1">
         <f>1.9068*357</f>
@@ -5130,7 +5130,7 @@
         <v>46075</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C33" s="1">
         <v>2823.3</v>
@@ -5144,7 +5144,7 @@
         <v>46075</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C34" s="1">
         <v>24191.29</v>
@@ -5158,7 +5158,7 @@
         <v>46075</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C35" s="1">
         <v>47343.93</v>
@@ -5172,7 +5172,7 @@
         <v>46075</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C36" s="1">
         <v>26033.46</v>
@@ -5215,7 +5215,7 @@
         <v>31</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.4">
@@ -5238,7 +5238,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.4">
@@ -5348,7 +5348,7 @@
         <v>46082</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C46" s="1">
         <v>1370.8</v>
@@ -5362,7 +5362,7 @@
         <v>46082</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C47" s="1">
         <v>923.89</v>
@@ -5376,7 +5376,7 @@
         <v>46082</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C48" s="1">
         <v>4001.91</v>
@@ -5390,7 +5390,7 @@
         <v>46082</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C49" s="1">
         <v>13784</v>
@@ -5404,7 +5404,7 @@
         <v>46082</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C50" s="1">
         <v>1685.84</v>
@@ -5418,7 +5418,7 @@
         <v>46082</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C51" s="1">
         <v>893.46</v>
@@ -5432,7 +5432,7 @@
         <v>46082</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C52" s="1">
         <v>16571.5</v>
@@ -5446,7 +5446,7 @@
         <v>46082</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>10</v>
@@ -5457,7 +5457,7 @@
         <v>46082</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C54" s="1">
         <v>47502.84</v>
@@ -5471,7 +5471,7 @@
         <v>46082</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C55" s="1">
         <v>26282.52</v>
